--- a/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,79</t>
+          <t>2,68; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,57; 21,71</t>
+          <t>15,39; 21,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,38</t>
+          <t>2,21; 5,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,13</t>
+          <t>3,08; 6,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 20,15</t>
+          <t>14,38; 20,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,64</t>
+          <t>3,58; 6,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,31</t>
+          <t>3,23; 5,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 19,95</t>
+          <t>15,69; 19,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,46</t>
+          <t>3,35; 5,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,46</t>
+          <t>1,99; 4,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 17,14</t>
+          <t>12,56; 17,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,46</t>
+          <t>3,84; 10,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,37</t>
+          <t>2,16; 4,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,24</t>
+          <t>11,69; 16,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,36</t>
+          <t>7,03; 10,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,99</t>
+          <t>2,27; 3,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,68; 15,96</t>
+          <t>12,77; 15,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,8</t>
+          <t>5,5; 9,79</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,62</t>
+          <t>5,66; 9,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 23,48</t>
+          <t>17,72; 23,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,03; 24,17</t>
+          <t>17,16; 24,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,33</t>
+          <t>3,92; 7,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 22,43</t>
+          <t>16,87; 22,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 22,45</t>
+          <t>7,14; 21,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,86</t>
+          <t>5,19; 7,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 22,08</t>
+          <t>17,92; 22,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 21,55</t>
+          <t>12,58; 21,82</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,3</t>
+          <t>1,88; 4,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,85</t>
+          <t>8,77; 13,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,75</t>
+          <t>8,98; 13,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,92</t>
+          <t>3,99; 6,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,89</t>
+          <t>7,97; 11,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 32,45</t>
+          <t>9,51; 30,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,09</t>
+          <t>3,25; 5,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 11,73</t>
+          <t>9,0; 11,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 26,2</t>
+          <t>10,13; 23,88</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,89</t>
+          <t>3,46; 4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,1</t>
+          <t>14,5; 17,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,9</t>
+          <t>8,29; 11,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,24</t>
+          <t>3,83; 5,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,83</t>
+          <t>13,45; 15,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,92</t>
+          <t>9,65; 16,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 4,89</t>
+          <t>3,83; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,18; 15,97</t>
+          <t>14,21; 16,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,83; 14,88</t>
+          <t>9,7; 14,15</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19287; 40716</t>
+          <t>18884; 40025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>105063; 146474</t>
+          <t>103879; 145631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15198; 34165</t>
+          <t>14025; 33809</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21312; 42733</t>
+          <t>21466; 44594</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95955; 135577</t>
+          <t>96742; 134848</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27089; 48131</t>
+          <t>25994; 48496</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45120; 74391</t>
+          <t>45250; 75898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>213544; 268875</t>
+          <t>211457; 267855</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45473; 74318</t>
+          <t>45621; 73420</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20593; 45371</t>
+          <t>20244; 44709</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128888; 175257</t>
+          <t>128412; 176575</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44449; 124832</t>
+          <t>45862; 125388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21675; 45123</t>
+          <t>22253; 46279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>122204; 169400</t>
+          <t>121947; 167439</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68229; 99287</t>
+          <t>67396; 97637</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46692; 81743</t>
+          <t>46484; 79877</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>261868; 329682</t>
+          <t>263652; 329692</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118833; 210766</t>
+          <t>118258; 210708</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40953; 72877</t>
+          <t>42890; 74357</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>131828; 178358</t>
+          <t>134562; 181188</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120000; 170324</t>
+          <t>120890; 172989</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29685; 56956</t>
+          <t>30457; 57854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>130625; 176093</t>
+          <t>132408; 179656</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82012; 209514</t>
+          <t>66616; 204688</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77988; 120625</t>
+          <t>79583; 121333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>277090; 341021</t>
+          <t>276711; 347597</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>200486; 352923</t>
+          <t>205993; 357377</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18145; 40758</t>
+          <t>17832; 38694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81708; 120507</t>
+          <t>82254; 122508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83362; 127395</t>
+          <t>83263; 128540</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42926; 72774</t>
+          <t>42017; 71555</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83706; 124148</t>
+          <t>83193; 123730</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>104808; 355342</t>
+          <t>104126; 339195</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65405; 101686</t>
+          <t>64998; 100089</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>176593; 232479</t>
+          <t>178325; 235450</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>207358; 529689</t>
+          <t>204809; 482843</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>120094; 167483</t>
+          <t>118571; 167116</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>488903; 580562</t>
+          <t>492038; 577072</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>281962; 411882</t>
+          <t>286686; 413730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135657; 186311</t>
+          <t>136385; 187873</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>473334; 561205</t>
+          <t>476803; 562513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>360218; 665407</t>
+          <t>358228; 630368</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>270685; 341272</t>
+          <t>267675; 337458</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>984256; 1108322</t>
+          <t>986040; 1118529</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>705061; 1067406</t>
+          <t>695414; 1014653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -51,34 +51,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -505,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,12 +485,6 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,67 +499,31 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -605,12 +535,6 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,47 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17,84%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -678,47 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,69</t>
+          <t>3,17; 6,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 21,58</t>
+          <t>4,44; 7,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,32</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,08; 6,4</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,38; 20,04</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,58; 6,69</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,23; 5,42</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15,69; 19,88</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3,35; 5,4</t>
+          <t>4,21; 6,49</t>
         </is>
       </c>
     </row>
@@ -735,47 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -788,47 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,39</t>
+          <t>8,23; 12,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 17,27</t>
+          <t>7,67; 10,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,51</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2,16; 4,48</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,69; 16,05</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,03; 10,18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,27; 3,9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12,77; 15,96</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5,5; 9,79</t>
+          <t>8,48; 11,09</t>
         </is>
       </c>
     </row>
@@ -845,47 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18,1%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -898,47 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,81</t>
+          <t>18,64; 25,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 23,85</t>
+          <t>21,11; 26,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,16; 24,55</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,92; 7,44</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>16,87; 22,89</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 21,93</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5,19; 7,91</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17,92; 22,5</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12,58; 21,82</t>
+          <t>20,87; 25,17</t>
         </is>
       </c>
     </row>
@@ -955,47 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,08</t>
+          <t>9,81; 14,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,07</t>
+          <t>9,43; 12,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 13,87</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3,99; 6,8</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,97; 11,85</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 30,98</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,25; 5,01</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9,0; 11,88</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10,13; 23,88</t>
+          <t>10,11; 13,0</t>
         </is>
       </c>
     </row>
@@ -1065,47 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,88</t>
+          <t>11,04; 13,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 17,0</t>
+          <t>11,2; 13,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,96</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3,83; 5,28</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,45; 15,87</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,65; 16,98</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,83; 4,83</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14,21; 16,12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9,7; 14,15</t>
+          <t>11,46; 13,01</t>
         </is>
       </c>
     </row>
@@ -1170,13 +794,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
+  <mergeCells count="6">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
@@ -1191,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1199,12 +820,6 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1219,67 +834,31 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1291,12 +870,6 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1311,45 +884,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>92</t>
         </is>
@@ -1364,47 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125393</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30881</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>115038</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35812</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59344</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>240431</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58972</t>
+          <t>74754</t>
         </is>
       </c>
     </row>
@@ -1417,47 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18884; 40025</t>
+          <t>21882; 45737</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103879; 145631</t>
+          <t>32588; 54082</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14025; 33809</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21466; 44594</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>96742; 134848</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25994; 48496</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45250; 75898</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211457; 267855</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>45621; 73420</t>
+          <t>59953; 92460</t>
         </is>
       </c>
     </row>
@@ -1474,45 +957,15 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>132</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>218</t>
         </is>
@@ -1527,47 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>108914</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>151077</t>
+          <t>97262</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90507</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31862</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>144257</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82772</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>62220</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>295334</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>173280</t>
+          <t>206177</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20244; 44709</t>
+          <t>86281; 133521</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128412; 176575</t>
+          <t>82146; 116884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45862; 125388</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>22253; 46279</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>121947; 167439</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>67396; 97637</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>46484; 79877</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>263652; 329692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>118258; 210708</t>
+          <t>179776; 235189</t>
         </is>
       </c>
     </row>
@@ -1637,45 +1030,15 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>405</t>
         </is>
@@ -1690,47 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56034</t>
+          <t>175492</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>155593</t>
+          <t>194190</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143943</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42153</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>152581</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>152583</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98187</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>308174</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>296526</t>
+          <t>369683</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42890; 74357</t>
+          <t>149711; 204907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134562; 181188</t>
+          <t>171483; 217272</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120890; 172989</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30457; 57854</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>132408; 179656</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>66616; 204688</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>79583; 121333</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>276711; 347597</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>205993; 357377</t>
+          <t>337087; 406646</t>
         </is>
       </c>
     </row>
@@ -1800,45 +1103,15 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>164</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
@@ -1853,47 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>117561</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>101508</t>
+          <t>122233</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103861</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54680</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>102918</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>172658</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81941</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>204426</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>276519</t>
+          <t>239793</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17832; 38694</t>
+          <t>97089; 143919</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82254; 122508</t>
+          <t>105550; 143309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83263; 128540</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>42017; 71555</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>83193; 123730</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>104126; 339195</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>64998; 100089</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>178325; 235450</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204809; 482843</t>
+          <t>213233; 274110</t>
         </is>
       </c>
     </row>
@@ -1963,45 +1176,15 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>369</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>981</t>
         </is>
@@ -2016,47 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>142116</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>533571</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>159575</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>514794</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>443825</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>301691</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1048365</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
     </row>
@@ -2069,47 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>118571; 167116</t>
+          <t>390005; 481850</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>492038; 577072</t>
+          <t>418692; 492341</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>286686; 413730</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>136385; 187873</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>476803; 562513</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>358228; 630368</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>267675; 337458</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>986040; 1118529</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>695414; 1014653</t>
+          <t>833004; 945539</t>
         </is>
       </c>
     </row>
@@ -2121,14 +1244,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
+  <mergeCells count="6">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,62</t>
+          <t>30,17; 37,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,37</t>
+          <t>27,54; 33,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,49</t>
+          <t>29,42; 34,08</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 12,73</t>
+          <t>37,41; 44,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,91</t>
+          <t>39,35; 44,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,09</t>
+          <t>39,44; 43,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,64; 25,52</t>
+          <t>24,24; 31,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,11; 26,75</t>
+          <t>31,64; 37,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,87; 25,17</t>
+          <t>29,11; 34,16</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,54</t>
+          <t>44,83; 52,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 12,81</t>
+          <t>48,68; 53,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,0</t>
+          <t>47,84; 52,02</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 13,64</t>
+          <t>36,8; 40,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,17</t>
+          <t>39,47; 42,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 13,01</t>
+          <t>38,64; 40,93</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -884,17 +884,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>236</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>340</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>576</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>232924</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>221391</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74754</t>
+          <t>454316</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21882; 45737</t>
+          <t>208045; 260431</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32588; 54082</t>
+          <t>202166; 244232</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59953; 92460</t>
+          <t>418874; 485230</t>
         </is>
       </c>
     </row>
@@ -957,17 +957,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>390</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>988</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>108914</t>
+          <t>429157</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97262</t>
+          <t>450467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206177</t>
+          <t>879624</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86281; 133521</t>
+          <t>391835; 464197</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82146; 116884</t>
+          <t>420983; 477057</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>179776; 235189</t>
+          <t>835027; 926065</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1030,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>205</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>364</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>569</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>175492</t>
+          <t>223916</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>194190</t>
+          <t>283457</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>369683</t>
+          <t>507374</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>149711; 204907</t>
+          <t>194377; 252649</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>171483; 217272</t>
+          <t>256785; 308149</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>337087; 406646</t>
+          <t>469688; 551073</t>
         </is>
       </c>
     </row>
@@ -1103,17 +1103,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>490</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>766</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>1256</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>117561</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>122233</t>
+          <t>573760</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239793</t>
+          <t>1050649</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97089; 143919</t>
+          <t>442762; 514547</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105550; 143309</t>
+          <t>544407; 603657</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>213233; 274110</t>
+          <t>1007417; 1095390</t>
         </is>
       </c>
     </row>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>3389</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>434277</t>
+          <t>1362887</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>456129</t>
+          <t>1529076</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>890406</t>
+          <t>2891963</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>390005; 481850</t>
+          <t>1297904; 1432729</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>418692; 492341</t>
+          <t>1473565; 1583441</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>833004; 945539</t>
+          <t>2805564; 2971348</t>
         </is>
       </c>
     </row>
